--- a/data/trans_orig/Q24A01-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Q24A01-Clase-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Número medio de cigarrillos que fuman al día</t>
+          <t>Número medio de cigarrillos que fuman al día (tasa de respuesta: 99,44%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>13,94; 17,38</t>
+          <t>14,09; 17,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>13,01; 16,15</t>
+          <t>13,01; 16,18</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,74; 14,66</t>
+          <t>10,71; 14,52</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10,77; 16,01</t>
+          <t>10,94; 16,13</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>11,01; 14,32</t>
+          <t>10,9; 14,16</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,63; 12,19</t>
+          <t>9,56; 12,31</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,3; 11,06</t>
+          <t>8,43; 11,26</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,97; 9,23</t>
+          <t>6,99; 9,45</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>13,32; 15,71</t>
+          <t>13,31; 15,79</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11,95; 14,15</t>
+          <t>12,07; 14,34</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10,24; 12,88</t>
+          <t>10,25; 12,75</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9,64; 12,71</t>
+          <t>9,56; 12,74</t>
         </is>
       </c>
     </row>
@@ -856,52 +856,52 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>14,41; 17,48</t>
+          <t>14,51; 17,61</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>14,05; 17,89</t>
+          <t>13,96; 17,56</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,82; 13,98</t>
+          <t>10,96; 14,07</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10,97; 14,9</t>
+          <t>10,89; 14,74</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,95; 14,07</t>
+          <t>10,96; 13,88</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,24; 16,02</t>
+          <t>12,2; 15,98</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,27; 11,77</t>
+          <t>9,25; 11,83</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,33; 10,7</t>
+          <t>8,14; 10,69</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13,13; 15,39</t>
+          <t>13,11; 15,32</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13,5; 16,0</t>
+          <t>13,64; 16,2</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>10,1; 12,55</t>
+          <t>10,13; 12,42</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16,43; 18,73</t>
+          <t>16,39; 18,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15,22; 17,51</t>
+          <t>15,32; 17,52</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14,11; 16,73</t>
+          <t>14,12; 16,59</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13,75; 17,05</t>
+          <t>13,86; 17,2</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,88; 15,15</t>
+          <t>10,06; 15,52</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,68; 12,4</t>
+          <t>9,73; 12,39</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,76; 13,11</t>
+          <t>8,86; 13,22</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9,54; 14,22</t>
+          <t>9,7; 14,11</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>15,61; 17,74</t>
+          <t>15,68; 17,96</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>14,13; 16,19</t>
+          <t>14,22; 16,15</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13,46; 15,53</t>
+          <t>13,36; 15,61</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>13,44; 16,28</t>
+          <t>13,37; 16,21</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>16,98; 18,6</t>
+          <t>16,92; 18,58</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15,69; 17,56</t>
+          <t>15,65; 17,41</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14,02; 15,66</t>
+          <t>13,96; 15,7</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12,44; 14,48</t>
+          <t>12,41; 14,41</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>11,58; 13,6</t>
+          <t>11,52; 13,61</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,88; 13,7</t>
+          <t>11,88; 13,81</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,11; 11,79</t>
+          <t>10,21; 11,81</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,84; 10,17</t>
+          <t>8,8; 10,2</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>15,55; 16,89</t>
+          <t>15,54; 16,96</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14,42; 15,81</t>
+          <t>14,43; 15,86</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12,57; 13,82</t>
+          <t>12,57; 13,79</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11,19; 12,63</t>
+          <t>11,17; 12,63</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>15,4; 17,68</t>
+          <t>15,34; 17,64</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15,71; 18,39</t>
+          <t>15,56; 18,23</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13,54; 15,69</t>
+          <t>13,61; 15,64</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13,47; 16,81</t>
+          <t>13,54; 16,63</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>12,44; 14,7</t>
+          <t>12,27; 14,58</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,37; 14,47</t>
+          <t>12,32; 14,48</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,23; 13,17</t>
+          <t>11,08; 13,19</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>9,25; 11,1</t>
+          <t>9,4; 11,11</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>14,23; 15,86</t>
+          <t>14,23; 15,88</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14,43; 16,17</t>
+          <t>14,36; 16,01</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12,71; 14,18</t>
+          <t>12,68; 14,18</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>11,68; 13,54</t>
+          <t>11,81; 13,57</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11,15; 15,74</t>
+          <t>11,07; 15,46</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8,15; 12,24</t>
+          <t>8,02; 12,42</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8,47; 11,76</t>
+          <t>8,49; 12,13</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,22; 9,5</t>
+          <t>3,19; 9,7</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>10,88; 13,57</t>
+          <t>11,02; 13,77</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>11,24; 13,6</t>
+          <t>11,06; 13,58</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9,2; 11,55</t>
+          <t>9,25; 11,58</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8,16; 10,67</t>
+          <t>8,11; 10,57</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>11,4; 13,67</t>
+          <t>11,39; 13,66</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>10,87; 12,97</t>
+          <t>10,84; 12,93</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9,36; 11,33</t>
+          <t>9,29; 11,2</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>7,12; 9,61</t>
+          <t>7,08; 9,66</t>
         </is>
       </c>
     </row>
@@ -1556,37 +1556,37 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>16,36; 17,33</t>
+          <t>16,36; 17,35</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>15,52; 16,54</t>
+          <t>15,49; 16,59</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13,63; 14,62</t>
+          <t>13,62; 14,7</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12,96; 14,39</t>
+          <t>13,02; 14,41</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>12,06; 13,17</t>
+          <t>12,02; 13,19</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,09; 13,15</t>
+          <t>12,07; 13,09</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,46; 11,44</t>
+          <t>10,49; 11,44</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1596,22 +1596,22 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>14,83; 15,7</t>
+          <t>14,85; 15,64</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>14,16; 15,01</t>
+          <t>14,21; 15,01</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12,38; 13,09</t>
+          <t>12,39; 13,12</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>11,4; 12,33</t>
+          <t>11,46; 12,37</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q24A01-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Q24A01-Clase-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13,05</t>
+          <t>13,58</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>8,06</t>
+          <t>8,32</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>10,79</t>
+          <t>11,25</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>14,09; 17,61</t>
+          <t>13,98; 17,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>13,01; 16,18</t>
+          <t>12,98; 16,23</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,71; 14,52</t>
+          <t>10,73; 14,45</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10,94; 16,13</t>
+          <t>11,64; 17,32</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>10,9; 14,16</t>
+          <t>10,88; 14,11</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,56; 12,31</t>
+          <t>9,7; 12,41</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,43; 11,26</t>
+          <t>8,33; 11,05</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,99; 9,45</t>
+          <t>7,24; 9,62</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>13,31; 15,79</t>
+          <t>13,39; 15,75</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12,07; 14,34</t>
+          <t>12,05; 14,33</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10,25; 12,75</t>
+          <t>10,23; 12,88</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9,56; 12,74</t>
+          <t>10,12; 13,41</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12,85</t>
+          <t>13,11</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>9,47</t>
+          <t>9,53</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>11,24</t>
+          <t>11,33</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>14,51; 17,61</t>
+          <t>14,44; 17,63</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13,96; 17,56</t>
+          <t>13,97; 17,6</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,96; 14,07</t>
+          <t>10,91; 13,98</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10,89; 14,74</t>
+          <t>11,38; 15,08</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,96; 13,88</t>
+          <t>10,9; 13,95</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,2; 15,98</t>
+          <t>12,02; 15,71</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,25; 11,83</t>
+          <t>9,26; 11,89</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,14; 10,69</t>
+          <t>8,44; 10,81</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>13,11; 15,32</t>
+          <t>13,2; 15,4</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13,64; 16,2</t>
+          <t>13,57; 16,23</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10,42; 12,53</t>
+          <t>10,53; 12,55</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>10,13; 12,42</t>
+          <t>10,21; 12,5</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15,35</t>
+          <t>15,04</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>11,69</t>
+          <t>11,71</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>14,7</t>
+          <t>14,44</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16,39; 18,77</t>
+          <t>16,5; 18,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15,32; 17,52</t>
+          <t>15,33; 17,77</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14,12; 16,59</t>
+          <t>14,18; 16,63</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13,86; 17,2</t>
+          <t>13,46; 16,63</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10,06; 15,52</t>
+          <t>9,77; 15,02</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,73; 12,39</t>
+          <t>9,58; 12,51</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,86; 13,22</t>
+          <t>8,9; 13,13</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9,7; 14,11</t>
+          <t>9,75; 13,93</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>15,68; 17,96</t>
+          <t>15,69; 17,78</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>14,22; 16,15</t>
+          <t>14,2; 16,09</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13,36; 15,61</t>
+          <t>13,42; 15,68</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>13,37; 16,21</t>
+          <t>13,15; 15,91</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13,4</t>
+          <t>13,48</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>9,5</t>
+          <t>9,57</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>11,9</t>
+          <t>11,95</t>
         </is>
       </c>
     </row>
@@ -1136,42 +1136,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>16,92; 18,58</t>
+          <t>16,88; 18,66</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15,65; 17,41</t>
+          <t>15,6; 17,49</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13,96; 15,7</t>
+          <t>13,99; 15,61</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12,41; 14,41</t>
+          <t>12,43; 14,44</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>11,52; 13,61</t>
+          <t>11,56; 13,62</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,88; 13,81</t>
+          <t>11,79; 13,72</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,21; 11,81</t>
+          <t>10,14; 11,85</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>8,8; 10,2</t>
+          <t>8,89; 10,33</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1181,17 +1181,17 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14,43; 15,86</t>
+          <t>14,44; 15,76</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12,57; 13,79</t>
+          <t>12,57; 13,77</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11,17; 12,63</t>
+          <t>11,24; 12,66</t>
         </is>
       </c>
     </row>
@@ -1243,7 +1243,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>10,13</t>
+          <t>10,06</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>12,63</t>
+          <t>12,66</t>
         </is>
       </c>
     </row>
@@ -1276,69 +1276,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>15,34; 17,64</t>
+          <t>15,3; 17,64</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15,56; 18,23</t>
+          <t>15,82; 18,29</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13,61; 15,64</t>
+          <t>13,44; 15,73</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13,54; 16,63</t>
+          <t>13,72; 16,49</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>12,27; 14,58</t>
+          <t>12,38; 14,61</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,32; 14,48</t>
+          <t>12,47; 14,59</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,08; 13,19</t>
+          <t>11,21; 13,18</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>9,4; 11,11</t>
+          <t>9,2; 11,04</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>14,23; 15,88</t>
+          <t>14,16; 15,86</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14,36; 16,01</t>
+          <t>14,37; 16,13</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12,68; 14,18</t>
+          <t>12,71; 14,26</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>11,81; 13,57</t>
+          <t>11,84; 13,44</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1363,7 +1363,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5,22</t>
+          <t>5,52</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>9,38</t>
+          <t>9,42</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>8,41</t>
+          <t>8,59</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11,07; 15,46</t>
+          <t>11,27; 15,49</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8,02; 12,42</t>
+          <t>8,32; 12,46</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8,49; 12,13</t>
+          <t>8,5; 11,78</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,19; 9,7</t>
+          <t>3,49; 9,91</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>11,02; 13,77</t>
+          <t>10,85; 13,63</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>11,06; 13,58</t>
+          <t>11,25; 13,64</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9,25; 11,58</t>
+          <t>9,22; 11,58</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8,11; 10,57</t>
+          <t>8,29; 10,54</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>11,39; 13,66</t>
+          <t>11,43; 13,73</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>10,84; 12,93</t>
+          <t>10,8; 12,93</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9,29; 11,2</t>
+          <t>9,31; 11,24</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>7,08; 9,66</t>
+          <t>7,47; 9,84</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13,68</t>
+          <t>13,81</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>9,57</t>
+          <t>9,62</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>11,88</t>
+          <t>11,97</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>16,36; 17,35</t>
+          <t>16,33; 17,39</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>15,49; 16,59</t>
+          <t>15,44; 16,54</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13,62; 14,7</t>
+          <t>13,67; 14,7</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13,02; 14,41</t>
+          <t>13,08; 14,5</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>12,02; 13,19</t>
+          <t>12,06; 13,2</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,07; 13,09</t>
+          <t>12,11; 13,09</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,49; 11,44</t>
+          <t>10,53; 11,46</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>9,16; 10,01</t>
+          <t>9,2; 10,11</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>14,85; 15,64</t>
+          <t>14,85; 15,63</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>14,21; 15,01</t>
+          <t>14,21; 14,97</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12,39; 13,12</t>
+          <t>12,36; 13,09</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>11,46; 12,37</t>
+          <t>11,52; 12,4</t>
         </is>
       </c>
     </row>
